--- a/tests/fixtures/List_of_Patients_Schedule.xlsx
+++ b/tests/fixtures/List_of_Patients_Schedule.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Medicare" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Medical" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Dental" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,7 +863,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Delacroix, Owen</t>
+          <t>Ashgrove, Petra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +872,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>46027</v>
+        <v>46209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -886,6 +887,38 @@
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>99213/90833</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Delacroix, Owen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2/32/26</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>F41.1, F32.9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>99213/90833</t>
         </is>
@@ -902,6 +935,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ins</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Billed</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Co-pay</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Co-pays Paid</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>DX</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>CPT Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bellweather, Colm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2/32/26</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>F41.1, F32.9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>90834</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bellweather, Colm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46183</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2/32/26</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>104.27</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>F41.1, F32.9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>90834</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
